--- a/Spatial_Data_Typology.xlsx
+++ b/Spatial_Data_Typology.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="30080" yWindow="600" windowWidth="30080" windowHeight="24460" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="181029" fullCalcOnLoad="1"/>
@@ -537,170 +537,170 @@
     <row r="3" ht="29" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Jurisdictional &amp; Political Boundaries</t>
+          <t>Boundaries, Tenure &amp; Governance</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Juris_Political_Boundaries</t>
+          <t>Boundaries_Tenure_Governance</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Provinces, states, international boundary, management units, municipal boundaries, population centers, census boundaries, congressional districts, constituencies, political boundaries</t>
+          <t>Provinces, states, international boundary, management units, First Nations lands, municipal boundaries, population centers, census boundaries, congressional districts, constituencies, political boundaries, parks, wilderness, WMAs, conservation easements, IPCAs, private conservation lands and easements, national forests, tenure holders, stewardship agreements</t>
         </is>
       </c>
     </row>
     <row r="4" ht="29" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Land Designations &amp; Tenure</t>
+          <t>Biodiversity &amp; Ecosystems</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Land_Designations_Tenure</t>
+          <t>Biodiversity_Ecosystems</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Parks, wilderness, WMAs, conservation easements, IPCAs, private conservation lands and easements, national forests, tenure holders, stewardship agreements, First Nations lands</t>
+          <t>Ecoregions, ecosystem classification, key biodiversity areas, ecological benchmarks, biophysical data, digital elevation models, LiDAR products, slope, aspect, hillshade</t>
         </is>
       </c>
     </row>
     <row r="5" ht="29" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Biodiversity &amp; Ecosystems</t>
+          <t>Climate Change</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Biodiversity_Ecosystems</t>
+          <t>Climate_Change</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Ecoregions, ecosystem classification, key biodiversity areas, ecological benchmarks, biophysical data, digital elevation models, LiDAR products, slope, aspect, hillshade</t>
+          <t>Climate normals, projections, refugia, climate velocity, resilient landscapes, carbon stocks, fire regime, natural disturbance regime</t>
         </is>
       </c>
     </row>
     <row r="6" ht="29" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Climate Resilience</t>
+          <t>Connectivity &amp; Wildlife Movement</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Climate_Resilience</t>
+          <t>Connectivity_Wildlife_Movement</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Climate normals, projections, refugia, climate velocity, resilient landscapes, carbon stocks, fire regime, natural disturbance regime</t>
+          <t>Corridors, linkages, resistance/permeability surfaces, telemetry, movement models, barrier analysis</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Connectivity &amp; Wildlife Movement</t>
+          <t>Species</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Connectivity_Wildlife_Movement</t>
+          <t>Species</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Corridors, linkages, resistance/permeability surfaces, telemetry, movement models, barrier analysis</t>
+          <t>Distributions, habitat models, critical habitat, wildlife surveys, key ranges, range distribution, fish habitat, movement and presence data (GPS/telemetry)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="29" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Species</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Species</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Distributions, habitat models, critical habitat, wildlife surveys, key ranges, range distribution, fish habitat, movement and presence data (GPS/telemetry)</t>
+          <t>Hydrology, watershed boundaries, aquatic connectivity, riparian areas, water quality</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Land Cover, Land Use &amp; Disturbance</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Land_Cover_Use_Disturbance</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Hydrology, watershed boundaries, aquatic connectivity, riparian areas, water quality</t>
+          <t>Land cover classification, change detection, NDVI/phenology, burn history, burn severity, insect/disease extent</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Land Cover, Land Use &amp; Disturbance</t>
+          <t>Human Dimensions of Conservation</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Land_Cover_Use_Disturbance</t>
+          <t>Human_Dimensions_Conservation</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Land cover classification, change detection, NDVI/phenology, burn history, burn severity, insect/disease extent</t>
+          <t>Governance research, community and stakeholder data, Indigenous-led research, public attitudes and perception surveys</t>
         </is>
       </c>
     </row>
     <row r="11" ht="29" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Human Dimensions</t>
+          <t>Threats &amp; Infrastructure</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Human_Dimensions</t>
+          <t>Threats_Infrastructure</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Human population demographics, socioeconomic data, governance research, community and stakeholder data, Indigenous-led research, public attitudes and perception surveys</t>
+          <t>Roads, railways, pipelines, utility corridors, resource extraction, development, cumulative effects, human footprint indices, barrier structures, trails</t>
         </is>
       </c>
     </row>
     <row r="12" ht="29" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Threats &amp; Infrastructure</t>
+          <t>Demographics &amp; Socioeconomic Data</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Threats_Infrastructure</t>
+          <t>Demographics_Socioeconomic</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Roads, railways, pipelines, utility corridors, resource extraction, development, cumulative effects, human footprint indices, barrier structures</t>
+          <t>Human population demographics, socioeconomic data</t>
         </is>
       </c>
     </row>
